--- a/Playwright_Testcase.xlsx
+++ b/Playwright_Testcase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
   <si>
     <t>＃</t>
   </si>
@@ -75,46 +75,8 @@
 2. Nhấn vào "Submit" button </t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Hiển thị text: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>✨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Success: Hello, {Nội dung đã nhập}! ngya vị trí Elements:  id="frame-output"
-Ví dụ: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>✨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Success: Hello, Test1!</t>
-    </r>
+    <t>Hiển thị text: Success: Hello, {Nội dung đã nhập}! ngya vị trí Elements:  id="frame-output"
+Ví dụ: Success: Hello, Test1!</t>
   </si>
   <si>
     <t>Load Nested Frames (A → B → C)</t>
@@ -124,6 +86,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hi</t>
     </r>
     <r>
@@ -174,27 +142,7 @@
     <t>Nhấn vào "Click button" button</t>
   </si>
   <si>
-    <r>
-      <t>Hiển thị text "</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>✨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Alpha Clicked!" ngay vị trí Elements: id="res-A"</t>
-    </r>
+    <t>Hiển thị text "Iframe A Clicked!" ngay vị trí Elements: id="res-A"</t>
   </si>
   <si>
     <t>Iframe Alpha_Open Iframe B</t>
@@ -214,6 +162,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hiển thị text "</t>
     </r>
     <r>
@@ -223,16 +177,16 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>✨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Beta Clicked!" ngay vị trí Elements: id="res-B"</t>
+      <t>Iframe B Clicked!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" ngay vị trí Elements: id="res-B"</t>
     </r>
   </si>
   <si>
@@ -253,6 +207,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hiển thị text "</t>
     </r>
     <r>
@@ -262,16 +222,16 @@
         <rFont val="Times New Roman"/>
         <charset val="134"/>
       </rPr>
-      <t>✨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Gamma Clicked!" ngay vị trí Elements: id="res-C"</t>
+      <t>Iframe C Clicked!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>" ngay vị trí Elements: id="res-C"</t>
     </r>
   </si>
   <si>
@@ -320,6 +280,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>1. Đóng popup
 2. Hiển thị text "</t>
     </r>
@@ -419,6 +385,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>1. Đóng Trigger Confirm
 2. Hiển thị text "</t>
     </r>
@@ -446,6 +418,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>1. Đóng Trigger Confirm
 2. Hiển thị text "</t>
     </r>
@@ -486,6 +464,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>1. Đóng Trigger Prompt
 2. Hiển thị text "</t>
     </r>
@@ -517,27 +501,8 @@
   </si>
   <si>
     <t>1. Đóng Trigger Prompt
-2. Hiển thị text "👤 Name:  {Nội dung đã nhập}"  ngay vị trí Elements: id="prompt-result"
-Ví dụ:  👤 Name: Tester1</t>
-  </si>
-  <si>
-    <t>Simulate Failure State</t>
-  </si>
-  <si>
-    <t>Nhấn vào "Simulate Failure State" button</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hiển thị text "💥 CRITICAL FAILURE EMULATED"  ngay vị trí Elements: id="failure-msg"</t>
-  </si>
-  <si>
-    <t>Reset State</t>
-  </si>
-  <si>
-    <t>1. Nhấn vào "Simulate Failure State" button
-2. Nhấn vào "Reset State" button</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hiển thị text "System Normal"  ngay vị trí Elements: id="failure-msg"</t>
+2. Hiển thị text "Name:  {Nội dung đã nhập}"  ngay vị trí Elements: id="prompt-result"
+Ví dụ:  Name: Tester1</t>
   </si>
   <si>
     <t>Submit Form_invalid1</t>
@@ -549,6 +514,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hiển thị text "</t>
     </r>
     <r>
@@ -596,6 +567,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Hiển thị text "</t>
     </r>
     <r>
@@ -635,6 +612,583 @@
       </rPr>
       <t xml:space="preserve"> Submitted: ABC</t>
     </r>
+  </si>
+  <si>
+    <t>Full Page Screenshot</t>
+  </si>
+  <si>
+    <t>Chụp trong mọi trường hợp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. Click button [Normal State]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Check text [System Normal] hiển thị </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. Tiến hành chụp màn hình</t>
+    </r>
+  </si>
+  <si>
+    <t>Có thể chụp được hình ảnh theo folder chỉ định, và chụp trong mọi trường hợp cả passed hoặc failed</t>
+  </si>
+  <si>
+    <t>Element Screenshot_Pass</t>
+  </si>
+  <si>
+    <t>Chỉ chụp trong TH passed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. Click button [Normal State]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Check text [System Normal] hiển thị </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. Tiến hành chụp màn hình (config chỉ chụp khi failed)</t>
+    </r>
+  </si>
+  <si>
+    <t>Có thể chụp được hình ảnh chỉ mỗi element yêu cầu và sẽ lưu theo folder chỉ định, chỉ chụp hình ảnh trong trường hợp failed</t>
+  </si>
+  <si>
+    <t>Element Screenshot_Failed</t>
+  </si>
+  <si>
+    <t>Chỉ chụp trong TH failed</t>
+  </si>
+  <si>
+    <t>1. Click button [Failure State]
+2. Check text [System Normal] hiển thị 
+2. Tiến hành chụp màn hình (config chỉ chụp khi failed)</t>
+  </si>
+  <si>
+    <t>Element Video</t>
+  </si>
+  <si>
+    <t>Quay video trong mọi trường hợp</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. Config để quay video </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Tiến hành click button [Play Sequence] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Tiến hành assert check status thay đổi đến "Sequence complete!"</t>
+    </r>
+  </si>
+  <si>
+    <t>Có thể quay video đủ ngay khi vừa thao tác trên màn hình bất kể testcase passed hay failed</t>
+  </si>
+  <si>
+    <t>Element Video_Pass</t>
+  </si>
+  <si>
+    <t>Chỉ quay trong TH passed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. Config để quay video </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Tiến hành click button [Play Sequence] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Đợi tối đa 10s để check text "Sequence complete!" hiển thị</t>
+    </r>
+  </si>
+  <si>
+    <t>Chỉ quay video trong trường hợp testcase failed, trường hợp passed thì không tạo video trong folder chỉ định</t>
+  </si>
+  <si>
+    <t>Element Video_Failed</t>
+  </si>
+  <si>
+    <t>Chỉ quay trong TH failed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. Config để quay video </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Tiến hành click button [Play Sequence] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Đợi tối đa 1s để check text "Sequence complete!" hiển thị</t>
+    </r>
+  </si>
+  <si>
+    <t>Tracing</t>
+  </si>
+  <si>
+    <t>Trace trong mọi TH</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.Tiến hành config tracing cho testcase theo precondition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Điền text vào 2 ô input [Tracing &amp; Submission] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Click button [Submit Form]</t>
+    </r>
+  </si>
+  <si>
+    <t>Hiển thị link tracing sau khi run passed hoặc failed testcase, có thể mở link lên và check nội dung hiển thị trong tracing</t>
+  </si>
+  <si>
+    <t>Tracing_Failed</t>
+  </si>
+  <si>
+    <t>Trace chỉ khi testcase failed</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.Tiến hành config tracing cho testcase theo precondition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Không điền text vào 2 ô input [Tracing &amp; Submission] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Click button [Submit Form]</t>
+    </r>
+  </si>
+  <si>
+    <t>Hiển thị link tracing sau khi run failed testcase, có thể mở link lên và check nội dung hiển thị trong tracing. Trường hợp passed thì không hiển thị link tracing</t>
+  </si>
+  <si>
+    <t>beforeAll</t>
+  </si>
+  <si>
+    <t>Tạo 1 hook beforeAll với nội dung là sẽ thông báo việc evidence sẽ được lưu vào vị trí nào</t>
+  </si>
+  <si>
+    <t>Có thể config để hiển thị hướng dẫn thông báo cho user biết được các info liên quan đến file testcase đang run</t>
+  </si>
+  <si>
+    <t>afterAll</t>
+  </si>
+  <si>
+    <t>Tạo 1 hook afterAll với nội dung là sẽ thông báo kết thúc session text</t>
+  </si>
+  <si>
+    <t>beforeEach</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1. Tạo 1 hook beforeEach với nội dung sẽ là chủ động đăng nhập vào [Hooks Demo] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Input [Record Name] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Click button [Create record]</t>
+    </r>
+  </si>
+  <si>
+    <t>Có thể tự động login trước khi vào testcase, testscript sẽ không cần gọi ra hàm login</t>
+  </si>
+  <si>
+    <t>afterEach</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1. Tạo 1 hook afterEach với mục đích xóa record đã tạo trên màn hình</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">2. Nhập username, password để login vào màn hình </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">3. Input [Record Name] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">4. Click button [Create record] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5. Check kết quả là record hiển thị thành công</t>
+    </r>
+  </si>
+  <si>
+    <t>Có thể tự động xóa record sau khi run thành công testcase, testscript sẽ không cần gọi ra hàm delete record</t>
   </si>
 </sst>
 </file>
@@ -647,7 +1201,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -685,6 +1239,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1223,134 +1783,134 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1370,7 +1930,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1383,7 +1943,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1712,7 +2287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.1111111111111" customWidth="1"/>
@@ -1736,7 +2311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:6">
+    <row r="2" ht="36.75" customHeight="1" spans="1:6">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1773,7 +2348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="36.15" spans="1:5">
+    <row r="4" ht="35.7" customHeight="1" spans="1:5">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1824,7 +2399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1" spans="1:5">
+    <row r="7" ht="36.75" customHeight="1" spans="1:5">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1875,7 +2450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" spans="1:5">
+    <row r="10" ht="36.75" customHeight="1" spans="1:5">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1909,7 +2484,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" spans="1:5">
+    <row r="12" ht="36.75" customHeight="1" spans="1:5">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -2161,7 +2736,7 @@
       <c r="D26" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="9" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2178,8 +2753,8 @@
       <c r="D27" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>85</v>
+      <c r="E27" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:5">
@@ -2187,16 +2762,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:5">
@@ -2204,65 +2779,235 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:5">
       <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>88</v>
+      <c r="E30" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:5">
       <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="B31" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="C31" s="15" t="s">
         <v>95</v>
       </c>
+      <c r="D31" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:5">
-      <c r="A32" s="4"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:5">
-      <c r="A33" s="4"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" spans="1:5">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" spans="1:5">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" ht="46.35" spans="1:5">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" ht="57.75" spans="1:5">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1" spans="1:5">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1" spans="1:5">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" spans="1:5">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1" spans="1:5">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1" spans="1:5">
+      <c r="A42" s="4"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" spans="1:5">
+      <c r="A43" s="4"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Playwright_Testcase.xlsx
+++ b/Playwright_Testcase.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="137">
   <si>
     <t>＃</t>
   </si>
@@ -669,7 +669,8 @@
     </r>
   </si>
   <si>
-    <t>Có thể chụp được hình ảnh theo folder chỉ định, và chụp trong mọi trường hợp cả passed hoặc failed</t>
+    <t>Có thể chụp được hình ảnh theo folder chỉ định, và chụp trong mọi trường hợp cả passed hoặc failed
+Hình ảnh chụp được sẽ toàn trang đang thao tác</t>
   </si>
   <si>
     <t>Element Screenshot_Pass</t>
@@ -678,56 +679,13 @@
     <t>Chỉ chụp trong TH passed</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1. Click button [Normal State]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">2. Check text [System Normal] hiển thị </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2. Tiến hành chụp màn hình (config chỉ chụp khi failed)</t>
-    </r>
-  </si>
-  <si>
-    <t>Có thể chụp được hình ảnh chỉ mỗi element yêu cầu và sẽ lưu theo folder chỉ định, chỉ chụp hình ảnh trong trường hợp failed</t>
+    <t>1. Click button [Normal State]
+2. Check text [System Normal] hiển thị 
+2. Tiến hành chụp màn hình (config chỉ chụp khi failed)</t>
+  </si>
+  <si>
+    <t>Có thể chụp được hình ảnh chỉ mỗi element yêu cầu và sẽ lưu theo folder chỉ định, chỉ chụp hình ảnh trong trường hợp failed
+Không có hình ảnh nào được chụp</t>
   </si>
   <si>
     <t>Element Screenshot_Failed</t>
@@ -741,6 +699,10 @@
 2. Tiến hành chụp màn hình (config chỉ chụp khi failed)</t>
   </si>
   <si>
+    <t>Có thể chụp được hình ảnh chỉ mỗi element yêu cầu và sẽ lưu theo folder chỉ định, chỉ chụp hình ảnh trong trường hợp failed
+Sẽ có hình ảnh chụp được lưu do testcase đang failed</t>
+  </si>
+  <si>
     <t>Element Video</t>
   </si>
   <si>
@@ -796,7 +758,8 @@
     </r>
   </si>
   <si>
-    <t>Có thể quay video đủ ngay khi vừa thao tác trên màn hình bất kể testcase passed hay failed</t>
+    <t>Có thể quay video đủ ngay khi vừa thao tác trên màn hình bất kể testcase passed hay failed
+Video hiển thị đủ step</t>
   </si>
   <si>
     <t>Element Video_Pass</t>
@@ -854,7 +817,8 @@
     </r>
   </si>
   <si>
-    <t>Chỉ quay video trong trường hợp testcase failed, trường hợp passed thì không tạo video trong folder chỉ định</t>
+    <t>Chỉ quay video trong trường hợp testcase failed, trường hợp passed thì không tạo video trong folder chỉ định
+Testcase passed nên không có video</t>
   </si>
   <si>
     <t>Element Video_Failed</t>
@@ -912,6 +876,9 @@
     </r>
   </si>
   <si>
+    <t>Chỉ quay video trong trường hợp testcase failed, trường hợp passed thì không tạo video trong folder chỉ định</t>
+  </si>
+  <si>
     <t>Tracing</t>
   </si>
   <si>
@@ -967,13 +934,25 @@
     </r>
   </si>
   <si>
-    <t>Hiển thị link tracing sau khi run passed hoặc failed testcase, có thể mở link lên và check nội dung hiển thị trong tracing</t>
+    <t>Hiển thị link tracing sau khi run passed hoặc failed testcase, có thể mở link lên và check nội dung hiển thị trong tracing
+1. Check hiển thị message "Submitted: {Text đã nhập ở step 2}
+2. Trace được lưu và hiển thị đủ steps</t>
   </si>
   <si>
     <t>Tracing_Failed</t>
   </si>
   <si>
     <t>Trace chỉ khi testcase failed</t>
+  </si>
+  <si>
+    <t>1.Tiến hành config tracing cho testcase theo precondition
+2. Không điền text vào 2 ô input [Tracing &amp; Submission] 
+3. Click button [Submit Form]</t>
+  </si>
+  <si>
+    <t>Hiển thị link tracing sau khi run failed testcase, có thể mở link lên và check nội dung hiển thị trong tracing. Trường hợp passed thì không hiển thị link tracing
+1. Check hiển thị message "Both fields are required" 
+2. Trace được lưu và hiển thị đủ steps do testcase failed</t>
   </si>
   <si>
     <r>
@@ -1025,7 +1004,9 @@
     </r>
   </si>
   <si>
-    <t>Hiển thị link tracing sau khi run failed testcase, có thể mở link lên và check nội dung hiển thị trong tracing. Trường hợp passed thì không hiển thị link tracing</t>
+    <t>Hiển thị link tracing sau khi run failed testcase, có thể mở link lên và check nội dung hiển thị trong tracing. Trường hợp passed thì không hiển thị link tracing
+1. Check hiển thị message "Submitted: {Text đã nhập ở step 2}
+2. Không có file tracing</t>
   </si>
   <si>
     <t>beforeAll</t>
@@ -1034,13 +1015,127 @@
     <t>Tạo 1 hook beforeAll với nội dung là sẽ thông báo việc evidence sẽ được lưu vào vị trí nào</t>
   </si>
   <si>
-    <t>Có thể config để hiển thị hướng dẫn thông báo cho user biết được các info liên quan đến file testcase đang run</t>
+    <t>Có thể config để hiển thị hướng dẫn thông báo cho user biết được các info liên quan đến file testcase đang run
+Khi tiến hành run file testcase sẽ hiển thị line thông báo ở terminal, line sẽ có dạng như là: 
+"[beforeAll] Setup môi trường test
+Artifacts sẽ được lưu tại: xxxxxxx "</t>
   </si>
   <si>
     <t>afterAll</t>
   </si>
   <si>
     <t>Tạo 1 hook afterAll với nội dung là sẽ thông báo kết thúc session text</t>
+  </si>
+  <si>
+    <t>Có thể config để hiển thị hướng dẫn thông báo cho user biết được các info liên quan đến file testcase đang run
+Khi hoàn thành run file testcase sẽ hiển thị line thông báo ở terminal, line sẽ có dạng như là: 
+"[afterAll] Kết thúc test session – dọn dẹp môi trường "</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">
+---------
+Nhập Record Name: Text "Name1"
+Category chọn Bug
+Nhấn vào button Create Record
+Expect:
+"hk-create-msg" sẽ hiển thị thông báo "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> "{Record Name đã nhập}" created at 19:08:39 (beforeEach done)."
+"hk-sub" sẽ hiện record đã tạo. Nội dung các cột "Name" và "Category" hiển thị chính xác
+---------
+Nhập Record Name: Text "Name2"
+Category chọn Feature
+Nhấn vào button Create Record
+Expect:
+"hk-create-msg" sẽ hiển thị thông báo "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> "{Record Name đã nhập}" created at 19:08:39 (beforeEach done)."
+"hk-sub" sẽ hiện record đã tạo. Nội dung các cột "Name" và "Category" hiển thị chính xác
+---------
+Nhập Record Name: Text "Name3"
+Category chọn Task
+Nhấn vào button Create Record
+Expect:
+"hk-create-msg" sẽ hiển thị thông báo "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> "{Record Name đã nhập}" created at 19:08:39 (beforeEach done)."
+"hk-sub" sẽ hiện record đã tạo. Nội dung các cột "Name" và "Category" hiển thị chính xác
+---------
+Nhập Record Name: Text "Name3"
+Category chọn Chore
+Nhấn vào button Create Record
+Expect:
+"hk-create-msg" sẽ hiển thị thông báo "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> "{Record Name đã nhập}" created at 19:08:39 (beforeEach done)."
+"hk-sub" sẽ hiện record đã tạo. Nội dung các cột "Name" và "Category" hiển thị chính xác
+---------</t>
+    </r>
   </si>
   <si>
     <t>beforeEach</t>
@@ -1095,7 +1190,8 @@
     </r>
   </si>
   <si>
-    <t>Có thể tự động login trước khi vào testcase, testscript sẽ không cần gọi ra hàm login</t>
+    <t>Có thể tự động login trước khi vào testcase, testscript sẽ không cần gọi ra hàm login
+Hiển thị record được tạo thành công ở trên màn hình</t>
   </si>
   <si>
     <t>afterEach</t>
@@ -1188,7 +1284,8 @@
     </r>
   </si>
   <si>
-    <t>Có thể tự động xóa record sau khi run thành công testcase, testscript sẽ không cần gọi ra hàm delete record</t>
+    <t>Có thể tự động xóa record sau khi run thành công testcase, testscript sẽ không cần gọi ra hàm delete record
+Sau khi testcase passed thì hệ thống sẽ tự động xóa record đã tạo trên màn hình</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1298,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1239,12 +1336,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1783,134 +1874,134 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1955,11 +2046,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2287,11 +2384,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.1111111111111" customWidth="1"/>
     <col min="2" max="5" width="37.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="28.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.15" spans="1:5">
@@ -2791,7 +2889,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1" spans="1:5">
+    <row r="30" ht="34.95" spans="1:6">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -2807,8 +2905,9 @@
       <c r="E30" s="12" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="31" ht="36" customHeight="1" spans="1:5">
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" ht="46.35" spans="1:6">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -2824,183 +2923,207 @@
       <c r="E31" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="32" ht="36" customHeight="1" spans="1:5">
+      <c r="F31" s="15"/>
+    </row>
+    <row r="32" ht="57.75" spans="1:6">
       <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="15" t="s">
         <v>99</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>100</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1" spans="1:5">
+        <v>101</v>
+      </c>
+      <c r="F32" s="15"/>
+    </row>
+    <row r="33" ht="36" customHeight="1" spans="1:6">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1" spans="1:5">
+        <v>105</v>
+      </c>
+      <c r="F33" s="15"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" spans="1:6">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" spans="1:5">
+        <v>109</v>
+      </c>
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" ht="36" customHeight="1" spans="1:6">
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="17" t="s">
+      <c r="B35" s="6" t="s">
         <v>110</v>
       </c>
+      <c r="C35" s="15" t="s">
+        <v>111</v>
+      </c>
       <c r="D35" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" ht="46.35" spans="1:5">
+        <v>113</v>
+      </c>
+      <c r="F35" s="15"/>
+    </row>
+    <row r="36" ht="80.55" spans="1:6">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" ht="57.75" spans="1:5">
+        <v>117</v>
+      </c>
+      <c r="F36" s="16"/>
+    </row>
+    <row r="37" ht="103.35" spans="1:6">
       <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="B37" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="C37" s="18" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="38" ht="36" customHeight="1" spans="1:5">
+      <c r="D37" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="16"/>
+    </row>
+    <row r="38" ht="91.95" spans="1:6">
       <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>122</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1" spans="1:5">
+        <v>123</v>
+      </c>
+      <c r="F38" s="16"/>
+    </row>
+    <row r="39" ht="91.95" spans="1:6">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1" spans="1:5">
+        <v>126</v>
+      </c>
+      <c r="F39" s="16"/>
+    </row>
+    <row r="40" ht="409.5" spans="1:6">
       <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1" spans="1:5">
+        <v>129</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" ht="57.75" spans="1:6">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1" spans="1:5">
-      <c r="A42" s="4"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
+        <v>133</v>
+      </c>
+      <c r="F41" s="15"/>
+    </row>
+    <row r="42" ht="80.55" spans="1:6">
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="15"/>
     </row>
     <row r="43" ht="36" customHeight="1" spans="1:5">
       <c r="A43" s="4"/>
@@ -3009,9 +3132,16 @@
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
     </row>
+    <row r="44" ht="36" customHeight="1" spans="1:5">
+      <c r="A44" s="4"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="https://bsv-nhungnguyen.github.io/"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://bsv-nhungnguyen.github.io/" tooltip="https://bsv-nhungnguyen.github.io/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
